--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-rang-de-la-vaccination.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4332,7 +4332,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>167</v>
       </c>
@@ -4347,13 +4347,13 @@
         <v>62</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>74</v>
@@ -4435,7 +4435,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>171</v>
       </c>
@@ -4450,13 +4450,13 @@
         <v>172</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -4744,7 +4744,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>185</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
